--- a/tests/teststratergy/TestSratergy.xlsx
+++ b/tests/teststratergy/TestSratergy.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rukmal/Projects/demo-msupply/tests/teststratergy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59B35761-719B-304E-84F5-9FFAA4F8DAF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21387B54-BE3F-044A-BE35-92EE2B25DA87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16340" xr2:uid="{B293C058-C882-4F47-9632-92A45EE27B93}"/>
+    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16340" activeTab="1" xr2:uid="{B293C058-C882-4F47-9632-92A45EE27B93}"/>
   </bookViews>
   <sheets>
-    <sheet name="Test Stratergy" sheetId="1" r:id="rId1"/>
+    <sheet name="Test Stratergy v.0" sheetId="1" r:id="rId1"/>
+    <sheet name="Test Stratergy v1.0" sheetId="3" r:id="rId2"/>
+    <sheet name="Analysis" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="72">
   <si>
     <t>Open mSupply – Test Strategy (Revamp Release)</t>
   </si>
@@ -85,9 +87,6 @@
   </si>
   <si>
     <t>Test Approach &amp; Coverage</t>
-  </si>
-  <si>
-    <t>Functional Testing</t>
   </si>
   <si>
     <t>New features: redesigned UI, improved search/filter, inline validation, new reporting capabilities.</t>
@@ -303,13 +302,371 @@
       </rPr>
       <t>Non‑critical bespoke reports, deprecated modules.</t>
     </r>
+  </si>
+  <si>
+    <t>ERPNext</t>
+  </si>
+  <si>
+    <t>Issue Guidline'</t>
+  </si>
+  <si>
+    <t>Bug Report Guidelines</t>
+  </si>
+  <si>
+    <t>OpenLMIS</t>
+  </si>
+  <si>
+    <t>Test Strategy</t>
+  </si>
+  <si>
+    <t>OpenLMIS, like many software projects, relies on testing to guide development and prevent regressions. To effect this we've adopted a standard set of tools to write and execute our tests, and categorize them to understand what types of tests we have, who writes them, when they're written, run, and where they live.</t>
+  </si>
+  <si>
+    <t>Unit tests</t>
+  </si>
+  <si>
+    <t>Who: written by code-author during implementation
+What: the smallest unit (e.g. one piece of a model's behavior, a function, etc)
+When: at build time, should be /fast/ and targetted - I can run just a portion of the test suite
+Where: Reside inside a service, next to unit under test. Generally able to access package-private scope
+Why: to test fundamental pieces/functionality, helps guide and document design and refactors, protects against regression</t>
+  </si>
+  <si>
+    <t>Who: Code author during implementation
+What: Test basic operation of a service to persistent storage or a service to another service. When another service is required, a test-double should be used, not the actual service.
+When: As explicitly asked for, these tests are typically slower and therefore need to be kept seperate from build to not slow development. Will be run in CI on every change.
+Where: Reside inside a service, seperated from other types of tests/code.
+Why: Ensures that the basic pathways to a service's external run-time dependancies work. e.g. that a db schema supports the ORM, or a non-responsive service call is gracefully handled.</t>
+  </si>
+  <si>
+    <t>End-to-End</t>
+  </si>
+  <si>
+    <t>Who: QA / developer with input from BA.
+What: Typical/core business scenarios.
+When: Ran in CI.
+Where: Resides in seperate repository.
+Why: Ensures all the pieces are working together to carry-out a business scenario. Helps ensure end-users can achieve their goals.</t>
+  </si>
+  <si>
+    <t>Integration Testing</t>
+  </si>
+  <si>
+    <t>Functional Testing: End-to-End</t>
+  </si>
+  <si>
+    <t>Data Sync Testing</t>
+  </si>
+  <si>
+    <t>Load Testing</t>
+  </si>
+  <si>
+    <t>Open mSupply – Test Strategy</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">General Issue Guidelines
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Search existing Issues:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Before raising a Issue, search if it has been raised before. Maybe add a 👍 or give additional help by creating a mockup if it is not already created.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Report each issue separately:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Don't club multiple, unreleated issues in one note.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Brief:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Please don't include long explanations. Use screenshots and bullet points instead of descriptive paragraphs.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Clear Title:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Add a clear subject to your bug report like "Unable to submit Purchase Order without Basic Rate" instead of just "Cannot Submit"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Version Number:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Please add version numbers of Frappe and ERPNext in your report. Often a bug is fixed in the latest version. It's usually helpful to provide the version number of your browser as well.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Steps to Reproduce:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The bug report must have a list of steps needed to reproduce a bug. If we cannot reproduce it, then we cannot solve it.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Actual behavior: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">After describing steps to reproduce, please explain what exactly fails or behaves wrong, according to your opinion.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Expected behavior: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Describe what and how should be done in a proper way.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Screenshots: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Screenshots are a great way of communicating the issues. Try adding annotations or using a tool like LiceCAP to take a screencast in gif</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">API / Integration Testing:
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner: Developer/QAE
+What:Test basic operation of a service to persistent storage or a service to another service. When another service is required, a test-double should be used, not the actual service.
+When: Ran in CI.
+Why:
+How: Test Framework/API
+Where: Resides in seperate repository.
+</t>
+  </si>
+  <si>
+    <t>Owner:
+What: Legacy parity (exploratory + charters): Legacy parity (exploratory + charters) for each in-scope functional area and ned ehhancements.
+When: Dev branch
+Why:
+How: Manual and Automation for regression
+Where: Resides in seperate repository.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>In‑scope:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Core supply chain flows:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Supporting Modules: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Settings, users/roles, multi‑language UI, reporting/analytics, and 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Data Sync</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> from legacy mSupply.</t>
+    </r>
+  </si>
+  <si>
+    <t>Date: 15--9-2025</t>
+  </si>
+  <si>
+    <t>3. Data Sync accuracy &amp; reversibility: e.g., “large volume + schema changes + downtime constraints”</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -337,13 +694,48 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="14"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -355,10 +747,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -368,8 +761,16 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -423,6 +824,55 @@
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="952500" cy="1054100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1901</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>27453</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8690A4F2-A33C-5246-A130-2ADE53BE5CD2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="954401" cy="1056153"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -789,12 +1239,12 @@
     </row>
     <row r="11" spans="1:2" ht="119" x14ac:dyDescent="0.2">
       <c r="B11" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="B12" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
@@ -814,7 +1264,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
@@ -834,186 +1284,506 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
-        <v>10</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="68" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B28" t="s">
-        <v>12</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="34" x14ac:dyDescent="0.2">
+      <c r="B28" s="2" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B29" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B32" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B35" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B37" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B38" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B41" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B42" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B45" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B48" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B49" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B50" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B51" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B54" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B55" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A57" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B58" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B59" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B60" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B61" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B62" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B63" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B64" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="65" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B65" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="66" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B66" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{625988DB-E538-7940-A663-C08AB331EE95}">
+  <dimension ref="A1:B67"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="12.5" style="4" customWidth="1"/>
+    <col min="2" max="2" width="66.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="27" x14ac:dyDescent="0.35">
+      <c r="B1" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="27" x14ac:dyDescent="0.35">
+      <c r="B2" s="1"/>
+    </row>
+    <row r="3" spans="1:2" ht="27" x14ac:dyDescent="0.35">
+      <c r="B3" s="1"/>
+    </row>
+    <row r="4" spans="1:2" ht="27" x14ac:dyDescent="0.35">
+      <c r="B4" s="1"/>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="34" x14ac:dyDescent="0.2">
+      <c r="B10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="85" x14ac:dyDescent="0.2">
+      <c r="B11" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="B12" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B17" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B19" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B20" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B21" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B25" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="119" x14ac:dyDescent="0.2">
+      <c r="B26" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B29" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="153" x14ac:dyDescent="0.2">
+      <c r="B30" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B32" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B35" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B36" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B37" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B38" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B39" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B40" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B41" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B42" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B43" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B49" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B50" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B51" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B52" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A54" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A58" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B59" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B60" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B61" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B62" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B63" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B64" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B65" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B66" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B67" t="s">
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BB6ED84-B9B5-F845-ABAD-C7C3178B9C24}">
+  <dimension ref="A2:D12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="26.6640625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="78.83203125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="79" style="5" customWidth="1"/>
+    <col min="4" max="16384" width="10.83203125" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:4" ht="53" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="8"/>
+    </row>
+    <row r="3" spans="1:4" ht="80" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="135" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="240" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="160" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="220" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="120" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{E0E8E5A2-5791-3E49-B9BE-2D5816E7F0E9}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>